--- a/stores picture/百禾.xlsx
+++ b/stores picture/百禾.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>五樣蔬菜飯盒</t>
   </si>
@@ -42,12 +42,6 @@
     <t>紅麴叉燒飯盒</t>
   </si>
   <si>
-    <t>鹹魚雙拼飯盒</t>
-  </si>
-  <si>
-    <t>台式鹹魚飯盒</t>
-  </si>
-  <si>
     <t>椒鹽雞排飯盒</t>
   </si>
   <si>
@@ -61,6 +55,9 @@
   </si>
   <si>
     <t>商業會議餐盒</t>
+  </si>
+  <si>
+    <t>海陸雙拼飯盒</t>
   </si>
 </sst>
 </file>
@@ -430,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -438,7 +435,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -446,7 +443,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -454,23 +451,23 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -499,7 +496,7 @@
     </row>
     <row r="9" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1">
         <v>110</v>
@@ -507,31 +504,31 @@
     </row>
     <row r="10" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="B12" s="1">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1">
         <v>130</v>
@@ -539,17 +536,9 @@
     </row>
     <row r="14" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1">
         <v>260</v>
       </c>
     </row>
